--- a/etf_gold_miners_uplift/rawGLD/GDXJ.xlsx
+++ b/etf_gold_miners_uplift/rawGLD/GDXJ.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GDXJ_asof_20260508" sheetId="1" r:id="R3b5e62221e814f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GDXJ_asof_20260513" sheetId="1" r:id="Rf145b61cb4064f14"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="637">
-  <x:si>
-    <x:t>All Holdings  05/08/2026</x:t>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="639">
+  <x:si>
+    <x:t>All Holdings  05/13/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -37,6 +37,24 @@
     <x:t>% of Net Assets</x:t>
   </x:si>
   <x:si>
+    <x:t>Coeur Mining Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CDE US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US1921085049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,569,713</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 90,206,135.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.42%</x:t>
+  </x:si>
+  <x:si>
     <x:t>Alamos Gold Inc</x:t>
   </x:si>
   <x:si>
@@ -46,31 +64,13 @@
     <x:t>CA0115321089</x:t>
   </x:si>
   <x:si>
-    <x:t>2,047,962</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 88,840,592.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.56%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Coeur Mining Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CDE US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US1921085049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,550,316</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 84,453,865.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.24%</x:t>
+    <x:t>2,056,692</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 89,774,606.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.39%</x:t>
   </x:si>
   <x:si>
     <x:t>Endeavour Mining Plc</x:t>
@@ -82,13 +82,13 @@
     <x:t>GB00BL6K5J42</x:t>
   </x:si>
   <x:si>
-    <x:t>1,285,782</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 84,040,673.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.21%</x:t>
+    <x:t>1,291,263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 85,875,256.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.11%</x:t>
   </x:si>
   <x:si>
     <x:t>Equinox Gold Corp</x:t>
@@ -100,13 +100,13 @@
     <x:t>CA29446Y5020</x:t>
   </x:si>
   <x:si>
-    <x:t>5,855,513</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 83,675,281.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6.18%</x:t>
+    <x:t>5,880,474</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 85,208,068.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.06%</x:t>
   </x:si>
   <x:si>
     <x:t>Evolution Mining Ltd</x:t>
@@ -118,13 +118,13 @@
     <x:t>AU000000EVN4</x:t>
   </x:si>
   <x:si>
-    <x:t>8,574,629</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 81,065,136.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.99%</x:t>
+    <x:t>8,611,181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 83,744,163.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.96%</x:t>
   </x:si>
   <x:si>
     <x:t>Industrias Penoles Sab De Cv</x:t>
@@ -136,13 +136,13 @@
     <x:t>MXP554091415</x:t>
   </x:si>
   <x:si>
-    <x:t>697,015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 41,157,385.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.04%</x:t>
+    <x:t>699,985</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 43,291,993.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.08%</x:t>
   </x:si>
   <x:si>
     <x:t>First Majestic Silver Corp</x:t>
@@ -154,13 +154,31 @@
     <x:t>CA32076V1031</x:t>
   </x:si>
   <x:si>
-    <x:t>1,673,787</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 36,588,984.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.70%</x:t>
+    <x:t>1,680,922</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 40,308,510.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.87%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hecla Mining Co</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HL US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US4227041062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,557,309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 32,781,354.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.33%</x:t>
   </x:si>
   <x:si>
     <x:t>Iamgold Corp</x:t>
@@ -172,31 +190,13 @@
     <x:t>CA4509131088</x:t>
   </x:si>
   <x:si>
-    <x:t>1,605,623</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 30,025,150.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.22%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hecla Mining Co</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HL US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US4227041062</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,550,699</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 28,858,508.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.13%</x:t>
+    <x:t>1,612,467</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 30,298,255.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.16%</x:t>
   </x:si>
   <x:si>
     <x:t>Lundin Gold Inc</x:t>
@@ -208,13 +208,49 @@
     <x:t>CA5503711080</x:t>
   </x:si>
   <x:si>
-    <x:t>378,808</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 26,558,893.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.96%</x:t>
+    <x:t>380,423</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 26,826,282.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.91%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Oceanagold Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OGC CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA6752224007</x:t>
+  </x:si>
+  <x:si>
+    <x:t>776,045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 26,637,350.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.90%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eldorado Gold Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EGO US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA2849025093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>737,670</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 26,216,792.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.87%</x:t>
   </x:si>
   <x:si>
     <x:t>Harmony Gold Mining Co Ltd</x:t>
@@ -226,49 +262,67 @@
     <x:t>US4132163001</x:t>
   </x:si>
   <x:si>
-    <x:t>1,473,087</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 26,206,218.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.94%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Eldorado Gold Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EGO US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA2849025093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>734,539</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 25,084,507.00</x:t>
+    <x:t>1,479,366</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 25,962,873.00</x:t>
   </x:si>
   <x:si>
     <x:t>1.85%</x:t>
   </x:si>
   <x:si>
-    <x:t>Oceanagold Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OGC CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA6752224007</x:t>
-  </x:si>
-  <x:si>
-    <x:t>772,751</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 24,637,047.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.82%</x:t>
+    <x:t>Cia De Minas Buenaventura Saa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BVN US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US2044481040</x:t>
+  </x:si>
+  <x:si>
+    <x:t>648,905</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 24,963,375.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.78%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B2gold Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BTG US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA11777Q2099</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,214,976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 22,592,271.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.61%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G Mining Ventures Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMIN CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA36270K1021</x:t>
+  </x:si>
+  <x:si>
+    <x:t>581,371</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 22,496,336.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.60%</x:t>
   </x:si>
   <x:si>
     <x:t>Zhaojin Mining Industry Co Ltd</x:t>
@@ -280,67 +334,13 @@
     <x:t>CNE1000004R6</x:t>
   </x:si>
   <x:si>
-    <x:t>6,128,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 23,404,251.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.73%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cia De Minas Buenaventura Saa</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BVN US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US2044481040</x:t>
-  </x:si>
-  <x:si>
-    <x:t>646,150</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 22,847,864.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.69%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G Mining Ventures Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMIN CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA36270K1021</x:t>
-  </x:si>
-  <x:si>
-    <x:t>578,903</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 22,710,452.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.68%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B2gold Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BTG US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA11777Q2099</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,197,085</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 22,244,551.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.64%</x:t>
+    <x:t>6,154,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 22,195,089.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.58%</x:t>
   </x:si>
   <x:si>
     <x:t>Ssr Mining Inc</x:t>
@@ -352,13 +352,13 @@
     <x:t>CA7847301032</x:t>
   </x:si>
   <x:si>
-    <x:t>598,356</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 20,463,775.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.51%</x:t>
+    <x:t>600,907</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 20,881,518.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.49%</x:t>
   </x:si>
   <x:si>
     <x:t>Dundee Precious Metals Inc</x:t>
@@ -370,13 +370,13 @@
     <x:t>CA26139R1091</x:t>
   </x:si>
   <x:si>
-    <x:t>571,343</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 19,763,936.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.46%</x:t>
+    <x:t>573,779</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 20,096,605.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.43%</x:t>
   </x:si>
   <x:si>
     <x:t>Greatland Resources Ltd</x:t>
@@ -388,13 +388,13 @@
     <x:t>AU0000397705</x:t>
   </x:si>
   <x:si>
-    <x:t>1,682,147</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 18,157,601.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.34%</x:t>
+    <x:t>1,689,317</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 18,255,464.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.30%</x:t>
   </x:si>
   <x:si>
     <x:t>Discovery Silver Corp</x:t>
@@ -406,13 +406,13 @@
     <x:t>CA2546771072</x:t>
   </x:si>
   <x:si>
-    <x:t>2,315,975</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 16,374,726.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.21%</x:t>
+    <x:t>2,325,848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 17,514,504.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.25%</x:t>
   </x:si>
   <x:si>
     <x:t>Or Royalties Inc</x:t>
@@ -424,13 +424,13 @@
     <x:t>CA68390D1069</x:t>
   </x:si>
   <x:si>
-    <x:t>412,722</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 15,856,779.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.17%</x:t>
+    <x:t>414,482</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 16,247,694.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.16%</x:t>
   </x:si>
   <x:si>
     <x:t>Ramelius Resources Ltd</x:t>
@@ -442,13 +442,31 @@
     <x:t>AU000000RMS4</x:t>
   </x:si>
   <x:si>
-    <x:t>6,100,097</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 15,555,632.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.15%</x:t>
+    <x:t>6,126,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 15,916,741.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.13%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>K92 Mining Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KNT CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA4991131083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>703,682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 14,454,120.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.03%</x:t>
   </x:si>
   <x:si>
     <x:t>Aris Mining Corp</x:t>
@@ -460,13 +478,13 @@
     <x:t>CA04040Y1097</x:t>
   </x:si>
   <x:si>
-    <x:t>713,177</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 14,049,587.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.04%</x:t>
+    <x:t>716,217</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 14,116,637.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.00%</x:t>
   </x:si>
   <x:si>
     <x:t>Torex Gold Resources Inc</x:t>
@@ -478,31 +496,61 @@
     <x:t>CA8910546032</x:t>
   </x:si>
   <x:si>
-    <x:t>274,905</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 13,772,357.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.02%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>K92 Mining Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KNT CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA4991131083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>700,695</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 13,613,678.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.01%</x:t>
+    <x:t>276,076</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 13,944,311.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.99%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perseus Mining Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PRU AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000PRU3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,392,303</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 13,910,096.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Artemis Gold Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTG CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA04302L1004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>503,624</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 13,207,521.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.94%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Genesis Minerals Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GMD AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000GMD9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,739,380</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 13,201,017.00</x:t>
   </x:si>
   <x:si>
     <x:t>Orla Mining Ltd</x:t>
@@ -514,66 +562,30 @@
     <x:t>CA68634K1066</x:t>
   </x:si>
   <x:si>
-    <x:t>899,664</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 13,530,947.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.00%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perseus Mining Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PRU AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000PRU3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,377,904</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 13,508,112.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Artemis Gold Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTG CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA04302L1004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>501,487</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 12,516,113.00</x:t>
+    <x:t>903,499</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 13,173,015.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Silvercorp Metals Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SVM US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA82835P1036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>827,496</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 12,999,962.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.92%</x:t>
   </x:si>
   <x:si>
-    <x:t>Genesis Minerals Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GMD AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000GMD9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,727,752</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 12,291,462.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.91%</x:t>
-  </x:si>
-  <x:si>
     <x:t>Centerra Gold Inc</x:t>
   </x:si>
   <x:si>
@@ -583,13 +595,100 @@
     <x:t>CA1520061021</x:t>
   </x:si>
   <x:si>
-    <x:t>656,034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 12,064,465.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.89%</x:t>
+    <x:t>658,831</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 12,438,729.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.88%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Capricorn Metals Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CMM AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000CMM9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,180,809</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 12,134,725.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.86%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Endeavour Silver Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EXK US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA29258Y1034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,041,521</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 11,748,357.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.84%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bumi Resources Minerals Tbk Pt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRMS IJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID1000117609</x:t>
+  </x:si>
+  <x:si>
+    <x:t>265,631,200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 11,711,195.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.83%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skeena Resources Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKE US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA83056P7157</x:t>
+  </x:si>
+  <x:si>
+    <x:t>340,883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 11,695,696.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wesdome Gold Mines Ltd/Canada</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WDO CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA95083R1001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>507,129</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 11,456,612.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.82%</x:t>
   </x:si>
   <x:si>
     <x:t>Aura Minerals Inc</x:t>
@@ -601,67 +700,31 @@
     <x:t>VGG069731120</x:t>
   </x:si>
   <x:si>
-    <x:t>143,370</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 11,772,111.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.87%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Capricorn Metals Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CMM AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000CMM9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,175,796</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 11,610,104.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bumi Resources Minerals Tbk Pt</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRMS IJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID1000117609</x:t>
-  </x:si>
-  <x:si>
-    <x:t>264,503,600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 11,423,997.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Silvercorp Metals Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SVM US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA82835P1036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>823,983</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 11,123,771.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.82%</x:t>
+    <x:t>143,981</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 11,411,934.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.81%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Montage Gold Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAU CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA61178L1013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>969,166</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 11,095,782.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.79%</x:t>
   </x:si>
   <x:si>
     <x:t>Pan African Resources Plc</x:t>
@@ -673,99 +736,33 @@
     <x:t>GB0004300496</x:t>
   </x:si>
   <x:si>
-    <x:t>5,294,844</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 10,903,980.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.81%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skeena Resources Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKE US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA83056P7157</x:t>
-  </x:si>
-  <x:si>
-    <x:t>339,436</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 10,797,459.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.80%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Endeavour Silver Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EXK US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA29258Y1034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,037,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 10,402,113.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.77%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wesdome Gold Mines Ltd/Canada</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WDO CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA95083R1001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>504,976</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 10,360,657.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Montage Gold Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAU CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA61178L1013</x:t>
-  </x:si>
-  <x:si>
-    <x:t>965,052</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 10,220,768.00</x:t>
+    <x:t>5,317,414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 10,743,397.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.76%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vault Minerals Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAU AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU0000427775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,006,704</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 10,517,796.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.75%</x:t>
   </x:si>
   <x:si>
-    <x:t>Vault Minerals Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VAU AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU0000427775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,993,941</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 10,194,111.00</x:t>
-  </x:si>
-  <x:si>
     <x:t>Westgold Resources Ltd</x:t>
   </x:si>
   <x:si>
@@ -775,10 +772,13 @@
     <x:t>AU000000WGX6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,502,920</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 10,154,143.00</x:t>
+    <x:t>2,513,589</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 10,343,425.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.74%</x:t>
   </x:si>
   <x:si>
     <x:t>Merdeka Gold Resources Tbk Pt</x:t>
@@ -790,13 +790,46 @@
     <x:t>ID1000211600</x:t>
   </x:si>
   <x:si>
-    <x:t>22,336,800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 9,936,757.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.73%</x:t>
+    <x:t>22,432,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 10,146,739.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.72%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hochschild Mining Plc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOC LN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GB00B1FW5029</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,098,770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 10,142,090.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Perpetua Resources Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPTA US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA7142661031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>312,676</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 9,933,717.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.71%</x:t>
   </x:si>
   <x:si>
     <x:t>Fortuna Silver Mines Inc</x:t>
@@ -808,13 +841,13 @@
     <x:t>CA3499421020</x:t>
   </x:si>
   <x:si>
-    <x:t>911,158</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 9,804,060.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.72%</x:t>
+    <x:t>915,042</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 9,781,799.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.70%</x:t>
   </x:si>
   <x:si>
     <x:t>Regis Resources Ltd</x:t>
@@ -826,43 +859,10 @@
     <x:t>AU000000RRL8</x:t>
   </x:si>
   <x:si>
-    <x:t>1,949,504</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 9,674,376.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.71%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hochschild Mining Plc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HOC LN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GB00B1FW5029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,094,106</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 9,555,862.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Perpetua Resources Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPTA US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA7142661031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>311,349</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 9,324,903.00</x:t>
+    <x:t>1,957,814</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 9,761,469.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.69%</x:t>
@@ -877,13 +877,10 @@
     <x:t>CA89679M1041</x:t>
   </x:si>
   <x:si>
-    <x:t>269,705</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 9,002,753.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.66%</x:t>
+    <x:t>270,855</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 9,637,021.00</x:t>
   </x:si>
   <x:si>
     <x:t>Seabridge Gold Inc</x:t>
@@ -895,10 +892,13 @@
     <x:t>CA8119161054</x:t>
   </x:si>
   <x:si>
-    <x:t>287,775</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 8,981,458.00</x:t>
+    <x:t>289,002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 9,612,207.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.68%</x:t>
   </x:si>
   <x:si>
     <x:t>Aya Gold &amp; Silver Inc</x:t>
@@ -910,10 +910,28 @@
     <x:t>CA05466C1095</x:t>
   </x:si>
   <x:si>
-    <x:t>437,389</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 8,446,837.00</x:t>
+    <x:t>439,253</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 9,397,569.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.67%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hycroft Mining Holding Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HYMC US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US44862P2083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>201,255</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 8,780,756.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.62%</x:t>
@@ -928,13 +946,79 @@
     <x:t>CA01921D2041</x:t>
   </x:si>
   <x:si>
-    <x:t>280,311</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 8,294,402.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.61%</x:t>
+    <x:t>281,506</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 8,307,242.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.59%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Emerald Resources Nl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMR AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000EMR4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,806,934</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 8,209,253.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.58%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Novagold Resources Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NG US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA66987E2069</x:t>
+  </x:si>
+  <x:si>
+    <x:t>903,969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 8,189,959.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Predictive Discovery Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PDI AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000PDI8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,816,280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 8,085,412.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Abrasilver Resource Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ABRA CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA00379L3048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>551,492</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 7,653,966.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.54%</x:t>
   </x:si>
   <x:si>
     <x:t>Wanguo Gold Group Ltd</x:t>
@@ -946,100 +1030,10 @@
     <x:t>KYG9430L1150</x:t>
   </x:si>
   <x:si>
-    <x:t>4,788,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 8,115,773.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.60%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Emerald Resources Nl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMR AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000EMR4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,799,264</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 7,951,206.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.59%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Novagold Resources Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NG US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA66987E2069</x:t>
-  </x:si>
-  <x:si>
-    <x:t>900,131</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 7,876,146.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.58%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hycroft Mining Holding Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HYMC US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US44862P2083</x:t>
-  </x:si>
-  <x:si>
-    <x:t>200,401</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 7,703,414.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.57%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Predictive Discovery Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PDI AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000PDI8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,770,368</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 7,373,448.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.54%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Abrasilver Resource Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ABRA CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA00379L3048</x:t>
-  </x:si>
-  <x:si>
-    <x:t>549,151</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 7,368,274.00</x:t>
+    <x:t>4,808,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 7,565,188.00</x:t>
   </x:si>
   <x:si>
     <x:t>West African Resources Ltd</x:t>
@@ -1051,15 +1045,33 @@
     <x:t>AU000000WAF6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,940,859</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 6,753,699.00</x:t>
+    <x:t>2,953,396</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 7,094,744.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.50%</x:t>
   </x:si>
   <x:si>
+    <x:t>Americas Gold &amp; Silver Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>USAS US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA03062D8035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>948,477</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 6,876,458.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.49%</x:t>
+  </x:si>
+  <x:si>
     <x:t>Southern Cross Gold Consolidated Ltd</x:t>
   </x:si>
   <x:si>
@@ -1069,28 +1081,13 @@
     <x:t>CA8426851090</x:t>
   </x:si>
   <x:si>
-    <x:t>859,898</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 6,261,912.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.46%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Americas Gold &amp; Silver Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>USAS US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA03062D8035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>944,451</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 6,261,710.00</x:t>
+    <x:t>863,564</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 6,698,300.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.48%</x:t>
   </x:si>
   <x:si>
     <x:t>Snowline Gold Corp</x:t>
@@ -1102,13 +1099,64 @@
     <x:t>CA83342V1040</x:t>
   </x:si>
   <x:si>
-    <x:t>447,323</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 5,172,101.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.38%</x:t>
+    <x:t>449,230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 5,497,163.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.39%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Resolute Mining Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RSG AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000RSG6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,205,757</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 5,232,638.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.37%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ora Banda Mining Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OBM AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU0000050130</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,116,627</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 5,143,048.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>G2 Goldfields Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GTWO CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA36256R1055</x:t>
+  </x:si>
+  <x:si>
+    <x:t>571,215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 5,022,541.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.36%</x:t>
   </x:si>
   <x:si>
     <x:t>Kingsgate Consolidated Ltd</x:t>
@@ -1120,61 +1168,28 @@
     <x:t>AU000000KCN1</x:t>
   </x:si>
   <x:si>
-    <x:t>997,085</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 5,013,026.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.37%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>G2 Goldfields Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GTWO CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA36256R1055</x:t>
-  </x:si>
-  <x:si>
-    <x:t>568,790</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 5,006,150.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ora Banda Mining Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OBM AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU0000050130</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5,094,908</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 4,982,856.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Resolute Mining Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RSG AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000RSG6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5,183,660</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 4,844,339.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.36%</x:t>
+    <x:t>1,001,335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 4,992,558.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Avino Silver &amp; Gold Mines Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASM US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA0539061030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>625,111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 4,894,619.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.35%</x:t>
   </x:si>
   <x:si>
     <x:t>Mcewen Mining Inc</x:t>
@@ -1186,13 +1201,10 @@
     <x:t>US58039P3055</x:t>
   </x:si>
   <x:si>
-    <x:t>187,806</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 4,550,539.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.34%</x:t>
+    <x:t>188,607</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 4,888,693.00</x:t>
   </x:si>
   <x:si>
     <x:t>Vizsla Silver Corp</x:t>
@@ -1204,46 +1216,49 @@
     <x:t>CA92859G6085</x:t>
   </x:si>
   <x:si>
-    <x:t>1,212,495</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 4,316,482.00</x:t>
+    <x:t>1,217,664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 4,688,006.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.33%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bellevue Gold Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BGL AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU0000019374</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,661,902</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 4,451,522.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.32%</x:t>
   </x:si>
   <x:si>
-    <x:t>Avino Silver &amp; Gold Mines Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASM US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA0539061030</x:t>
-  </x:si>
-  <x:si>
-    <x:t>622,457</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 4,294,953.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bellevue Gold Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BGL AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU0000019374</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,646,359</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 4,173,734.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.31%</x:t>
+    <x:t>Gogold Resources Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GGD CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA38045Y1025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,624,025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 4,206,858.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.30%</x:t>
   </x:si>
   <x:si>
     <x:t>I-80 Gold Corp</x:t>
@@ -1255,10 +1270,46 @@
     <x:t>CA44955L1067</x:t>
   </x:si>
   <x:si>
-    <x:t>2,633,540</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 4,160,993.00</x:t>
+    <x:t>2,644,766</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 4,125,835.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.29%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Koza Altin Isletmeleri As</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOZAL TI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TREKOAL00014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,599,911</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 3,722,215.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.26%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Catalyst Metals Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CYL AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000CYL6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>879,203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 3,630,684.00</x:t>
   </x:si>
   <x:si>
     <x:t>Chifeng Jilong Gold Mining Co Ltd</x:t>
@@ -1270,61 +1321,46 @@
     <x:t>CNE100006T51</x:t>
   </x:si>
   <x:si>
-    <x:t>661,800</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 3,863,205.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.29%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Gogold Resources Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GGD CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA38045Y1025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,617,132</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 3,543,493.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.26%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Koza Altin Isletmeleri As</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOZAL TI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TREKOAL00014</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,584,630</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 3,468,888.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Catalyst Metals Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CYL AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000CYL6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>875,471</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 3,456,579.00</x:t>
+    <x:t>664,600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 3,471,227.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.25%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alkane Resources Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALK AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000ALK9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,071,489</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 3,466,302.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Drdgold Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DRD US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US26152H3012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>110,504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 3,266,498.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.23%</x:t>
   </x:si>
   <x:si>
     <x:t>Tongguan Gold Group Ltd</x:t>
@@ -1336,43 +1372,28 @@
     <x:t>BMG8919D1074</x:t>
   </x:si>
   <x:si>
-    <x:t>8,724,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 3,454,476.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Alkane Resources Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALK AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000ALK9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,058,452</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 3,367,856.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.25%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Drdgold Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DRD US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US26152H3012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>110,035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 3,326,358.00</x:t>
+    <x:t>8,760,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 3,109,914.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.22%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Orezone Gold Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORE CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA68616T1093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,684,328</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 3,072,582.00</x:t>
   </x:si>
   <x:si>
     <x:t>Contango Ore Inc</x:t>
@@ -1384,13 +1405,28 @@
     <x:t>US21077F1003</x:t>
   </x:si>
   <x:si>
-    <x:t>112,599</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 3,061,567.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.23%</x:t>
+    <x:t>113,079</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,980,762.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.21%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dakota Gold Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DC US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>US46655E1001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>452,583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,905,583.00</x:t>
   </x:si>
   <x:si>
     <x:t>Collective Mining Ltd</x:t>
@@ -1402,45 +1438,15 @@
     <x:t>CA19425C1005</x:t>
   </x:si>
   <x:si>
-    <x:t>151,943</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 2,767,846.00</x:t>
+    <x:t>152,591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,755,757.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.20%</x:t>
   </x:si>
   <x:si>
-    <x:t>Orezone Gold Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ORE CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA68616T1093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,677,179</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 2,719,551.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dakota Gold Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DC US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>US46655E1001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>450,662</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 2,708,479.00</x:t>
-  </x:si>
-  <x:si>
     <x:t>Osisko Development Corp</x:t>
   </x:si>
   <x:si>
@@ -1450,10 +1456,10 @@
     <x:t>CA68828E8099</x:t>
   </x:si>
   <x:si>
-    <x:t>738,706</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 2,422,956.00</x:t>
+    <x:t>741,855</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,514,888.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.18%</x:t>
@@ -1468,10 +1474,10 @@
     <x:t>US6458272050</x:t>
   </x:si>
   <x:si>
-    <x:t>47,705</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 2,341,838.00</x:t>
+    <x:t>47,908</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,453,369.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.17%</x:t>
@@ -1486,10 +1492,10 @@
     <x:t>CA38071H1064</x:t>
   </x:si>
   <x:si>
-    <x:t>641,743</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 2,316,692.00</x:t>
+    <x:t>644,478</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,403,903.00</x:t>
   </x:si>
   <x:si>
     <x:t>Black Cat Syndicate Ltd</x:t>
@@ -1501,15 +1507,45 @@
     <x:t>AU000000BC88</x:t>
   </x:si>
   <x:si>
-    <x:t>2,363,999</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 2,063,681.00</x:t>
+    <x:t>2,374,076</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,084,813.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.15%</x:t>
   </x:si>
   <x:si>
+    <x:t>New Found Gold Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NFGC US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA64440N1033</x:t>
+  </x:si>
+  <x:si>
+    <x:t>917,969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,065,430.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Metalla Royalty &amp; Streaming Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MTA US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA59124U6051</x:t>
+  </x:si>
+  <x:si>
+    <x:t>268,664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,047,220.00</x:t>
+  </x:si>
+  <x:si>
     <x:t>Pantoro Gold Ltd</x:t>
   </x:si>
   <x:si>
@@ -1519,40 +1555,10 @@
     <x:t>AU000000PNR8</x:t>
   </x:si>
   <x:si>
-    <x:t>823,605</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 2,022,679.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>New Found Gold Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NFGC US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA64440N1033</x:t>
-  </x:si>
-  <x:si>
-    <x:t>914,072</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,992,677.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Metalla Royalty &amp; Streaming Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MTA US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA59124U6051</x:t>
-  </x:si>
-  <x:si>
-    <x:t>267,524</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,944,899.00</x:t>
+    <x:t>827,116</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 2,022,942.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.14%</x:t>
@@ -1567,10 +1573,46 @@
     <x:t>TREKOZA00014</x:t>
   </x:si>
   <x:si>
-    <x:t>695,019</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,887,508.00</x:t>
+    <x:t>697,981</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,942,550.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>St Barbara Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SBM AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000SBM8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,626,471</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,855,497.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.13%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Integra Resources Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ITRG US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA45826T5098</x:t>
+  </x:si>
+  <x:si>
+    <x:t>596,428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,687,891.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.12%</x:t>
   </x:si>
   <x:si>
     <x:t>Dateline Resources Ltd</x:t>
@@ -1582,46 +1624,10 @@
     <x:t>AU000000DTR1</x:t>
   </x:si>
   <x:si>
-    <x:t>10,331,279</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,796,278.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.13%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Integra Resources Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ITRG US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA45826T5098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>593,896</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,716,359.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>St Barbara Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SBM AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000SBM8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,611,078</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,687,349.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.12%</x:t>
+    <x:t>10,375,319</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,618,926.00</x:t>
   </x:si>
   <x:si>
     <x:t>Galiano Gold Inc</x:t>
@@ -1633,13 +1639,13 @@
     <x:t>CA36352H1001</x:t>
   </x:si>
   <x:si>
-    <x:t>562,194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,450,461.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.11%</x:t>
+    <x:t>564,591</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,473,583.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.10%</x:t>
   </x:si>
   <x:si>
     <x:t>Caledonia Mining Corp Plc</x:t>
@@ -1651,15 +1657,30 @@
     <x:t>JE00BF0XVB15</x:t>
   </x:si>
   <x:si>
-    <x:t>51,833</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,239,845.00</x:t>
+    <x:t>52,054</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,288,337.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.09%</x:t>
   </x:si>
   <x:si>
+    <x:t>Andean Precious Metals Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APM CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA03349X1015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>218,899</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,237,891.00</x:t>
+  </x:si>
+  <x:si>
     <x:t>Archi Indonesia Tbk Pt</x:t>
   </x:si>
   <x:si>
@@ -1669,10 +1690,73 @@
     <x:t>ID1000161003</x:t>
   </x:si>
   <x:si>
-    <x:t>15,064,600</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,201,524.00</x:t>
+    <x:t>15,128,800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,221,392.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aurelia Metals Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMI AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000AMI1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,629,686</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,159,198.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.08%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cnmc Goldmine Holdings Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CNMC SP</x:t>
+  </x:si>
+  <x:si>
+    <x:t> -- </x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,017,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,135,085.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Founders Metals Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FDR CN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA3505901056</x:t>
+  </x:si>
+  <x:si>
+    <x:t>264,439</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,121,085.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vox Royalty Corp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VOXR US</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA92919F1036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>171,949</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,079,840.00</x:t>
   </x:si>
   <x:si>
     <x:t>Gt Gold Holdings Ltd</x:t>
@@ -1684,43 +1768,43 @@
     <x:t>KYG4136P1303</x:t>
   </x:si>
   <x:si>
-    <x:t>16,416,000</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,153,280.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cnmc Goldmine Holdings Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CNMC SP</x:t>
-  </x:si>
-  <x:si>
-    <x:t> -- </x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,013,100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,127,043.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.08%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Founders Metals Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FDR CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA3505901056</x:t>
-  </x:si>
-  <x:si>
-    <x:t>263,316</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,096,269.00</x:t>
+    <x:t>16,488,000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,052,779.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.07%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Andean Silver Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASL AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU0000343253</x:t>
+  </x:si>
+  <x:si>
+    <x:t>589,675</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,044,214.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Antipa Minerals Ltd</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZY AU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AU000000AZY0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,011,285</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 1,014,485.00</x:t>
   </x:si>
   <x:si>
     <x:t>Meeka Metals Ltd</x:t>
@@ -1732,73 +1816,10 @@
     <x:t>AU0000192726</x:t>
   </x:si>
   <x:si>
-    <x:t>10,441,733</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,059,032.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Aurelia Metals Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMI AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000AMI1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,610,034</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,052,017.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Andean Precious Metals Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>APM CN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA03349X1015</x:t>
-  </x:si>
-  <x:si>
-    <x:t>217,970</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,042,804.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Vox Royalty Corp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VOXR US</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA92919F1036</x:t>
-  </x:si>
-  <x:si>
-    <x:t>171,219</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,018,753.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Antipa Minerals Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZY AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU000000AZY0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,002,747</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 1,008,368.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.07%</x:t>
+    <x:t>10,486,244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 989,351.00</x:t>
   </x:si>
   <x:si>
     <x:t>Goldmining Inc</x:t>
@@ -1810,25 +1831,10 @@
     <x:t>CA38149E1016</x:t>
   </x:si>
   <x:si>
-    <x:t>797,543</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 957,052.00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Andean Silver Ltd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASL AU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AU0000343253</x:t>
-  </x:si>
-  <x:si>
-    <x:t>587,172</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 906,052.00</x:t>
+    <x:t>800,943</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 977,150.00</x:t>
   </x:si>
   <x:si>
     <x:t>Us Gold Corp</x:t>
@@ -1840,10 +1846,10 @@
     <x:t>US90291C2017</x:t>
   </x:si>
   <x:si>
-    <x:t>48,023</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 815,911.00</x:t>
+    <x:t>48,227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 854,582.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.06%</x:t>
@@ -1858,10 +1864,10 @@
     <x:t>CA54929M1068</x:t>
   </x:si>
   <x:si>
-    <x:t>834,622</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 762,017.00</x:t>
+    <x:t>838,179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 831,788.00</x:t>
   </x:si>
   <x:si>
     <x:t>West Red Lake Gold Mines Ltd</x:t>
@@ -1873,10 +1879,10 @@
     <x:t>CA95556L1013</x:t>
   </x:si>
   <x:si>
-    <x:t>1,314,802</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 701,048.00</x:t>
+    <x:t>1,320,406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 703,343.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.05%</x:t>
@@ -1891,10 +1897,10 @@
     <x:t>ID1000094709</x:t>
   </x:si>
   <x:si>
-    <x:t>9,872,400</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$ 289,947.00</x:t>
+    <x:t>9,914,500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$ 283,839.00</x:t>
   </x:si>
   <x:si>
     <x:t>0.02%</x:t>
@@ -1912,13 +1918,13 @@
     <x:t>5,615,175</x:t>
   </x:si>
   <x:si>
-    <x:t>$ 247,329.00</x:t>
+    <x:t>$ 247,773.00</x:t>
   </x:si>
   <x:si>
     <x:t>Other/Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$ 1,095,057.00</x:t>
+    <x:t>$ 1,278,861.00</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2687,7 +2693,7 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7" ht="15" customHeight="1">
@@ -2695,22 +2701,22 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>171</x:v>
       </x:c>
-      <x:c r="C31" s="1" t="s">
+      <x:c r="D31" s="1" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
         <x:v>173</x:v>
       </x:c>
-      <x:c r="E31" s="1" t="s">
+      <x:c r="F31" s="1" t="s">
         <x:v>174</x:v>
       </x:c>
-      <x:c r="F31" s="1" t="s">
+      <x:c r="G31" s="1" t="s">
         <x:v>175</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7" ht="15" customHeight="1">
@@ -2733,7 +2739,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7" ht="15" customHeight="1">
@@ -2741,22 +2747,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
+      <x:c r="D33" s="1" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="D33" s="1" t="s">
+      <x:c r="E33" s="1" t="s">
         <x:v>184</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
+      <x:c r="F33" s="1" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>186</x:v>
-      </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7" ht="15" customHeight="1">
@@ -2764,22 +2770,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="D34" s="1" t="s">
         <x:v>188</x:v>
       </x:c>
-      <x:c r="C34" s="1" t="s">
+      <x:c r="E34" s="1" t="s">
         <x:v>189</x:v>
       </x:c>
-      <x:c r="D34" s="1" t="s">
+      <x:c r="F34" s="1" t="s">
         <x:v>190</x:v>
       </x:c>
-      <x:c r="E34" s="1" t="s">
+      <x:c r="G34" s="1" t="s">
         <x:v>191</x:v>
-      </x:c>
-      <x:c r="F34" s="1" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="G34" s="1" t="s">
-        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7" ht="15" customHeight="1">
@@ -2787,22 +2793,22 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="s">
+      <x:c r="E35" s="1" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
+      <x:c r="F35" s="1" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
+      <x:c r="G35" s="1" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="s">
-        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7" ht="15" customHeight="1">
@@ -2810,22 +2816,22 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
         <x:v>200</x:v>
       </x:c>
-      <x:c r="C36" s="1" t="s">
+      <x:c r="E36" s="1" t="s">
         <x:v>201</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="F36" s="1" t="s">
         <x:v>202</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
+      <x:c r="G36" s="1" t="s">
         <x:v>203</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="15" customHeight="1">
@@ -2833,22 +2839,22 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
         <x:v>206</x:v>
       </x:c>
-      <x:c r="C37" s="1" t="s">
+      <x:c r="E37" s="1" t="s">
         <x:v>207</x:v>
       </x:c>
-      <x:c r="D37" s="1" t="s">
+      <x:c r="F37" s="1" t="s">
         <x:v>208</x:v>
       </x:c>
-      <x:c r="E37" s="1" t="s">
+      <x:c r="G37" s="1" t="s">
         <x:v>209</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G37" s="1" t="s">
-        <x:v>211</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="15" customHeight="1">
@@ -2856,22 +2862,22 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
         <x:v>212</x:v>
       </x:c>
-      <x:c r="C38" s="1" t="s">
+      <x:c r="E38" s="1" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="F38" s="1" t="s">
         <x:v>214</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
+      <x:c r="G38" s="1" t="s">
         <x:v>215</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>217</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7" ht="15" customHeight="1">
@@ -2879,22 +2885,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
         <x:v>218</x:v>
       </x:c>
-      <x:c r="C39" s="1" t="s">
+      <x:c r="E39" s="1" t="s">
         <x:v>219</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
+      <x:c r="F39" s="1" t="s">
         <x:v>220</x:v>
       </x:c>
-      <x:c r="E39" s="1" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="s">
-        <x:v>222</x:v>
-      </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7" ht="15" customHeight="1">
@@ -2902,22 +2908,22 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="C40" s="1" t="s">
+      <x:c r="F40" s="1" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="D40" s="1" t="s">
+      <x:c r="G40" s="1" t="s">
         <x:v>226</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="G40" s="1" t="s">
-        <x:v>229</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7" ht="15" customHeight="1">
@@ -2925,22 +2931,22 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="C41" s="1" t="s">
+      <x:c r="F41" s="1" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="D41" s="1" t="s">
+      <x:c r="G41" s="1" t="s">
         <x:v>232</x:v>
-      </x:c>
-      <x:c r="E41" s="1" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="G41" s="1" t="s">
-        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="15" customHeight="1">
@@ -2948,22 +2954,22 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="D42" s="1" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="C42" s="1" t="s">
+      <x:c r="F42" s="1" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="D42" s="1" t="s">
+      <x:c r="G42" s="1" t="s">
         <x:v>238</x:v>
-      </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="G42" s="1" t="s">
-        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="15" customHeight="1">
@@ -2971,22 +2977,22 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="s">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="C43" s="1" t="s">
+      <x:c r="E43" s="1" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="F43" s="1" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
+      <x:c r="G43" s="1" t="s">
         <x:v>244</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7" ht="15" customHeight="1">
@@ -2994,22 +3000,22 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="D44" s="1" t="s">
         <x:v>247</x:v>
       </x:c>
-      <x:c r="C44" s="1" t="s">
+      <x:c r="E44" s="1" t="s">
         <x:v>248</x:v>
       </x:c>
-      <x:c r="D44" s="1" t="s">
+      <x:c r="F44" s="1" t="s">
         <x:v>249</x:v>
       </x:c>
-      <x:c r="E44" s="1" t="s">
+      <x:c r="G44" s="1" t="s">
         <x:v>250</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="G44" s="1" t="s">
-        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7" ht="15" customHeight="1">
@@ -3017,22 +3023,22 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="s">
         <x:v>252</x:v>
       </x:c>
-      <x:c r="C45" s="1" t="s">
+      <x:c r="D45" s="1" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="D45" s="1" t="s">
+      <x:c r="E45" s="1" t="s">
         <x:v>254</x:v>
       </x:c>
-      <x:c r="E45" s="1" t="s">
+      <x:c r="F45" s="1" t="s">
         <x:v>255</x:v>
       </x:c>
-      <x:c r="F45" s="1" t="s">
+      <x:c r="G45" s="1" t="s">
         <x:v>256</x:v>
-      </x:c>
-      <x:c r="G45" s="1" t="s">
-        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7" ht="15" customHeight="1">
@@ -3078,7 +3084,7 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="15" customHeight="1">
@@ -3086,22 +3092,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="s">
         <x:v>269</x:v>
       </x:c>
-      <x:c r="C48" s="1" t="s">
+      <x:c r="D48" s="1" t="s">
         <x:v>270</x:v>
       </x:c>
-      <x:c r="D48" s="1" t="s">
+      <x:c r="E48" s="1" t="s">
         <x:v>271</x:v>
       </x:c>
-      <x:c r="E48" s="1" t="s">
+      <x:c r="F48" s="1" t="s">
         <x:v>272</x:v>
       </x:c>
-      <x:c r="F48" s="1" t="s">
+      <x:c r="G48" s="1" t="s">
         <x:v>273</x:v>
-      </x:c>
-      <x:c r="G48" s="1" t="s">
-        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7" ht="15" customHeight="1">
@@ -3109,22 +3115,22 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>275</x:v>
       </x:c>
-      <x:c r="C49" s="1" t="s">
+      <x:c r="D49" s="1" t="s">
         <x:v>276</x:v>
       </x:c>
-      <x:c r="D49" s="1" t="s">
+      <x:c r="E49" s="1" t="s">
         <x:v>277</x:v>
       </x:c>
-      <x:c r="E49" s="1" t="s">
+      <x:c r="F49" s="1" t="s">
         <x:v>278</x:v>
       </x:c>
-      <x:c r="F49" s="1" t="s">
+      <x:c r="G49" s="1" t="s">
         <x:v>279</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7" ht="15" customHeight="1">
@@ -3170,7 +3176,7 @@
         <x:v>290</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>285</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7" ht="15" customHeight="1">
@@ -3178,22 +3184,22 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="s">
         <x:v>292</x:v>
       </x:c>
-      <x:c r="C52" s="1" t="s">
+      <x:c r="D52" s="1" t="s">
         <x:v>293</x:v>
       </x:c>
-      <x:c r="D52" s="1" t="s">
+      <x:c r="E52" s="1" t="s">
         <x:v>294</x:v>
       </x:c>
-      <x:c r="E52" s="1" t="s">
+      <x:c r="F52" s="1" t="s">
         <x:v>295</x:v>
       </x:c>
-      <x:c r="F52" s="1" t="s">
+      <x:c r="G52" s="1" t="s">
         <x:v>296</x:v>
-      </x:c>
-      <x:c r="G52" s="1" t="s">
-        <x:v>291</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7" ht="15" customHeight="1">
@@ -3308,7 +3314,7 @@
         <x:v>325</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7" ht="15" customHeight="1">
@@ -3316,22 +3322,22 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
         <x:v>327</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
+      <x:c r="D58" s="1" t="s">
         <x:v>328</x:v>
       </x:c>
-      <x:c r="D58" s="1" t="s">
+      <x:c r="E58" s="1" t="s">
         <x:v>329</x:v>
       </x:c>
-      <x:c r="E58" s="1" t="s">
+      <x:c r="F58" s="1" t="s">
         <x:v>330</x:v>
       </x:c>
-      <x:c r="F58" s="1" t="s">
-        <x:v>331</x:v>
-      </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7" ht="15" customHeight="1">
@@ -3339,22 +3345,22 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
         <x:v>333</x:v>
       </x:c>
-      <x:c r="C59" s="1" t="s">
+      <x:c r="E59" s="1" t="s">
         <x:v>334</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
+      <x:c r="F59" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
-      <x:c r="E59" s="1" t="s">
+      <x:c r="G59" s="1" t="s">
         <x:v>336</x:v>
-      </x:c>
-      <x:c r="F59" s="1" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="G59" s="1" t="s">
-        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7" ht="15" customHeight="1">
@@ -3362,22 +3368,22 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="C60" s="1" t="s">
+      <x:c r="E60" s="1" t="s">
         <x:v>340</x:v>
       </x:c>
-      <x:c r="D60" s="1" t="s">
+      <x:c r="F60" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
-      <x:c r="E60" s="1" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="F60" s="1" t="s">
-        <x:v>343</x:v>
-      </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7" ht="15" customHeight="1">
@@ -3385,22 +3391,22 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="D61" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="C61" s="1" t="s">
+      <x:c r="E61" s="1" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="D61" s="1" t="s">
+      <x:c r="F61" s="1" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="E61" s="1" t="s">
+      <x:c r="G61" s="1" t="s">
         <x:v>347</x:v>
-      </x:c>
-      <x:c r="F61" s="1" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="G61" s="1" t="s">
-        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7" ht="15" customHeight="1">
@@ -3408,22 +3414,22 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="C62" s="1" t="s">
+      <x:c r="E62" s="1" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="D62" s="1" t="s">
+      <x:c r="F62" s="1" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="E62" s="1" t="s">
+      <x:c r="G62" s="1" t="s">
         <x:v>353</x:v>
-      </x:c>
-      <x:c r="F62" s="1" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="G62" s="1" t="s">
-        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7" ht="15" customHeight="1">
@@ -3431,22 +3437,22 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="D63" s="1" t="s">
         <x:v>356</x:v>
       </x:c>
-      <x:c r="C63" s="1" t="s">
+      <x:c r="E63" s="1" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="D63" s="1" t="s">
+      <x:c r="F63" s="1" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="E63" s="1" t="s">
+      <x:c r="G63" s="1" t="s">
         <x:v>359</x:v>
-      </x:c>
-      <x:c r="F63" s="1" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="G63" s="1" t="s">
-        <x:v>355</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7" ht="15" customHeight="1">
@@ -3454,22 +3460,22 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="C64" s="1" t="s">
+      <x:c r="D64" s="1" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="D64" s="1" t="s">
+      <x:c r="E64" s="1" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="E64" s="1" t="s">
+      <x:c r="F64" s="1" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="F64" s="1" t="s">
+      <x:c r="G64" s="1" t="s">
         <x:v>365</x:v>
-      </x:c>
-      <x:c r="G64" s="1" t="s">
-        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7" ht="15" customHeight="1">
@@ -3477,22 +3483,22 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="C65" s="1" t="s">
+      <x:c r="D65" s="1" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="D65" s="1" t="s">
+      <x:c r="E65" s="1" t="s">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="E65" s="1" t="s">
+      <x:c r="F65" s="1" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="F65" s="1" t="s">
+      <x:c r="G65" s="1" t="s">
         <x:v>371</x:v>
-      </x:c>
-      <x:c r="G65" s="1" t="s">
-        <x:v>372</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7" ht="15" customHeight="1">
@@ -3500,22 +3506,22 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="C66" s="1" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="C66" s="1" t="s">
+      <x:c r="D66" s="1" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="D66" s="1" t="s">
+      <x:c r="E66" s="1" t="s">
         <x:v>375</x:v>
       </x:c>
-      <x:c r="E66" s="1" t="s">
+      <x:c r="F66" s="1" t="s">
         <x:v>376</x:v>
       </x:c>
-      <x:c r="F66" s="1" t="s">
-        <x:v>377</x:v>
-      </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>371</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7" ht="15" customHeight="1">
@@ -3523,22 +3529,22 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="C67" s="1" t="s">
+      <x:c r="D67" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
+      <x:c r="E67" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E67" s="1" t="s">
+      <x:c r="F67" s="1" t="s">
         <x:v>381</x:v>
       </x:c>
-      <x:c r="F67" s="1" t="s">
+      <x:c r="G67" s="1" t="s">
         <x:v>382</x:v>
-      </x:c>
-      <x:c r="G67" s="1" t="s">
-        <x:v>372</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7" ht="15" customHeight="1">
@@ -3561,7 +3567,7 @@
         <x:v>387</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>388</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7" ht="15" customHeight="1">
@@ -3569,22 +3575,22 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="C69" s="1" t="s">
         <x:v>389</x:v>
       </x:c>
-      <x:c r="C69" s="1" t="s">
+      <x:c r="D69" s="1" t="s">
         <x:v>390</x:v>
       </x:c>
-      <x:c r="D69" s="1" t="s">
+      <x:c r="E69" s="1" t="s">
         <x:v>391</x:v>
       </x:c>
-      <x:c r="E69" s="1" t="s">
+      <x:c r="F69" s="1" t="s">
         <x:v>392</x:v>
       </x:c>
-      <x:c r="F69" s="1" t="s">
+      <x:c r="G69" s="1" t="s">
         <x:v>393</x:v>
-      </x:c>
-      <x:c r="G69" s="1" t="s">
-        <x:v>394</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7" ht="15" customHeight="1">
@@ -3592,22 +3598,22 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="C70" s="1" t="s">
         <x:v>395</x:v>
       </x:c>
-      <x:c r="C70" s="1" t="s">
+      <x:c r="D70" s="1" t="s">
         <x:v>396</x:v>
       </x:c>
-      <x:c r="D70" s="1" t="s">
+      <x:c r="E70" s="1" t="s">
         <x:v>397</x:v>
       </x:c>
-      <x:c r="E70" s="1" t="s">
+      <x:c r="F70" s="1" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="F70" s="1" t="s">
-        <x:v>399</x:v>
-      </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>400</x:v>
+        <x:v>393</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7" ht="15" customHeight="1">
@@ -3615,22 +3621,22 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="C71" s="1" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="D71" s="1" t="s">
         <x:v>401</x:v>
       </x:c>
-      <x:c r="C71" s="1" t="s">
+      <x:c r="E71" s="1" t="s">
         <x:v>402</x:v>
       </x:c>
-      <x:c r="D71" s="1" t="s">
+      <x:c r="F71" s="1" t="s">
         <x:v>403</x:v>
       </x:c>
-      <x:c r="E71" s="1" t="s">
+      <x:c r="G71" s="1" t="s">
         <x:v>404</x:v>
-      </x:c>
-      <x:c r="F71" s="1" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="G71" s="1" t="s">
-        <x:v>400</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7" ht="15" customHeight="1">
@@ -3638,22 +3644,22 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="C72" s="1" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="C72" s="1" t="s">
+      <x:c r="D72" s="1" t="s">
         <x:v>407</x:v>
       </x:c>
-      <x:c r="D72" s="1" t="s">
+      <x:c r="E72" s="1" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="E72" s="1" t="s">
+      <x:c r="F72" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="F72" s="1" t="s">
+      <x:c r="G72" s="1" t="s">
         <x:v>410</x:v>
-      </x:c>
-      <x:c r="G72" s="1" t="s">
-        <x:v>411</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7" ht="15" customHeight="1">
@@ -3661,22 +3667,22 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="C73" s="1" t="s">
         <x:v>412</x:v>
       </x:c>
-      <x:c r="C73" s="1" t="s">
+      <x:c r="D73" s="1" t="s">
         <x:v>413</x:v>
       </x:c>
-      <x:c r="D73" s="1" t="s">
+      <x:c r="E73" s="1" t="s">
         <x:v>414</x:v>
       </x:c>
-      <x:c r="E73" s="1" t="s">
+      <x:c r="F73" s="1" t="s">
         <x:v>415</x:v>
       </x:c>
-      <x:c r="F73" s="1" t="s">
+      <x:c r="G73" s="1" t="s">
         <x:v>416</x:v>
-      </x:c>
-      <x:c r="G73" s="1" t="s">
-        <x:v>411</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7" ht="15" customHeight="1">
@@ -3768,7 +3774,7 @@
         <x:v>438</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>428</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7" ht="15" customHeight="1">
@@ -3776,22 +3782,22 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="C78" s="1" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="D78" s="1" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="E78" s="1" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="F78" s="1" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="G78" s="1" t="s">
         <x:v>439</x:v>
-      </x:c>
-      <x:c r="C78" s="1" t="s">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="D78" s="1" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="E78" s="1" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="F78" s="1" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="G78" s="1" t="s">
-        <x:v>428</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7" ht="15" customHeight="1">
@@ -3799,22 +3805,22 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>444</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>445</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>446</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>447</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="F79" s="1" t="s">
-        <x:v>448</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7" ht="15" customHeight="1">
@@ -3822,22 +3828,22 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>451</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>452</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>453</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F80" s="1" t="s">
-        <x:v>454</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>449</x:v>
+        <x:v>456</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7" ht="15" customHeight="1">
@@ -3845,22 +3851,22 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>457</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="D81" s="1" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="E81" s="1" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="F81" s="1" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="G81" s="1" t="s">
         <x:v>456</x:v>
-      </x:c>
-      <x:c r="D81" s="1" t="s">
-        <x:v>457</x:v>
-      </x:c>
-      <x:c r="E81" s="1" t="s">
-        <x:v>458</x:v>
-      </x:c>
-      <x:c r="F81" s="1" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="G81" s="1" t="s">
-        <x:v>460</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7" ht="15" customHeight="1">
@@ -3868,22 +3874,22 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>461</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>462</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>463</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>464</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="F82" s="1" t="s">
-        <x:v>465</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>467</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7" ht="15" customHeight="1">
@@ -3891,22 +3897,22 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="C83" s="1" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="D83" s="1" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="E83" s="1" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="F83" s="1" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="G83" s="1" t="s">
         <x:v>467</x:v>
-      </x:c>
-      <x:c r="C83" s="1" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="D83" s="1" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="E83" s="1" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="F83" s="1" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="G83" s="1" t="s">
-        <x:v>466</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7" ht="15" customHeight="1">
@@ -3914,22 +3920,22 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>473</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>474</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="F84" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>466</x:v>
+        <x:v>478</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7" ht="15" customHeight="1">
@@ -3937,22 +3943,22 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>477</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>479</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>480</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="F85" s="1" t="s">
-        <x:v>481</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>482</x:v>
+        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7" ht="15" customHeight="1">
@@ -3960,22 +3966,22 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>483</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>485</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="F86" s="1" t="s">
-        <x:v>487</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7" ht="15" customHeight="1">
@@ -3983,22 +3989,22 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="D87" s="1" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="E87" s="1" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="F87" s="1" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="G87" s="1" t="s">
         <x:v>490</x:v>
-      </x:c>
-      <x:c r="D87" s="1" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="E87" s="1" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="F87" s="1" t="s">
-        <x:v>493</x:v>
-      </x:c>
-      <x:c r="G87" s="1" t="s">
-        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7" ht="15" customHeight="1">
@@ -4006,22 +4012,22 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>494</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>496</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="F88" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7" ht="15" customHeight="1">
@@ -4029,22 +4035,22 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>500</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="D89" s="1" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="E89" s="1" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="F89" s="1" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="G89" s="1" t="s">
         <x:v>501</x:v>
-      </x:c>
-      <x:c r="D89" s="1" t="s">
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="E89" s="1" t="s">
-        <x:v>503</x:v>
-      </x:c>
-      <x:c r="F89" s="1" t="s">
-        <x:v>504</x:v>
-      </x:c>
-      <x:c r="G89" s="1" t="s">
-        <x:v>499</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7" ht="15" customHeight="1">
@@ -4052,22 +4058,22 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="F90" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>501</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7" ht="15" customHeight="1">
@@ -4075,22 +4081,22 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="F91" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>517</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7" ht="15" customHeight="1">
@@ -4098,22 +4104,22 @@
         <x:v>89</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="D92" s="1" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="E92" s="1" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="F92" s="1" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="G92" s="1" t="s">
         <x:v>517</x:v>
-      </x:c>
-      <x:c r="D92" s="1" t="s">
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="E92" s="1" t="s">
-        <x:v>519</x:v>
-      </x:c>
-      <x:c r="F92" s="1" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="G92" s="1" t="s">
-        <x:v>515</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7" ht="15" customHeight="1">
@@ -4121,22 +4127,22 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="F93" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>528</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7" ht="15" customHeight="1">
@@ -4144,22 +4150,22 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>527</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>528</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>529</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>530</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="F94" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>534</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7" ht="15" customHeight="1">
@@ -4167,22 +4173,22 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>532</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>533</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="E95" s="1" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="F95" s="1" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="G95" s="1" t="s">
         <x:v>534</x:v>
-      </x:c>
-      <x:c r="E95" s="1" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="F95" s="1" t="s">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c r="G95" s="1" t="s">
-        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7" ht="15" customHeight="1">
@@ -4190,22 +4196,22 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>538</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>539</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>540</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>541</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="F96" s="1" t="s">
-        <x:v>542</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7" ht="15" customHeight="1">
@@ -4213,22 +4219,22 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>544</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>545</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>546</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>547</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="F97" s="1" t="s">
-        <x:v>548</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>549</x:v>
+        <x:v>551</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7" ht="15" customHeight="1">
@@ -4236,22 +4242,22 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="D98" s="1" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="E98" s="1" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="F98" s="1" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="G98" s="1" t="s">
         <x:v>551</x:v>
-      </x:c>
-      <x:c r="D98" s="1" t="s">
-        <x:v>552</x:v>
-      </x:c>
-      <x:c r="E98" s="1" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="F98" s="1" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="G98" s="1" t="s">
-        <x:v>549</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7" ht="15" customHeight="1">
@@ -4259,22 +4265,22 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>557</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>558</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="F99" s="1" t="s">
-        <x:v>559</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>549</x:v>
+        <x:v>551</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7" ht="15" customHeight="1">
@@ -4282,22 +4288,22 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>560</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>563</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="F100" s="1" t="s">
-        <x:v>564</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>567</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7" ht="15" customHeight="1">
@@ -4305,22 +4311,22 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>566</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="D101" s="1" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="E101" s="1" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="F101" s="1" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="G101" s="1" t="s">
         <x:v>567</x:v>
-      </x:c>
-      <x:c r="D101" s="1" t="s">
-        <x:v>568</x:v>
-      </x:c>
-      <x:c r="E101" s="1" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="F101" s="1" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="G101" s="1" t="s">
-        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7" ht="15" customHeight="1">
@@ -4328,22 +4334,22 @@
         <x:v>99</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>571</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>573</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="F102" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>567</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7" ht="15" customHeight="1">
@@ -4351,22 +4357,22 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>576</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>577</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>578</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>579</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F103" s="1" t="s">
-        <x:v>580</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>567</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7" ht="15" customHeight="1">
@@ -4374,22 +4380,22 @@
         <x:v>101</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>581</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>582</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>583</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>584</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="F104" s="1" t="s">
-        <x:v>585</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7" ht="15" customHeight="1">
@@ -4397,22 +4403,22 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>586</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>587</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="E105" s="1" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="F105" s="1" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="G105" s="1" t="s">
         <x:v>588</x:v>
-      </x:c>
-      <x:c r="E105" s="1" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="F105" s="1" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="G105" s="1" t="s">
-        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7" ht="15" customHeight="1">
@@ -4420,22 +4426,22 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>592</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>594</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="F106" s="1" t="s">
-        <x:v>595</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>596</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7" ht="15" customHeight="1">
@@ -4443,22 +4449,22 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>598</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>599</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="F107" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>596</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7" ht="15" customHeight="1">
@@ -4466,22 +4472,22 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>602</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>603</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>604</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>605</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="F108" s="1" t="s">
-        <x:v>606</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>596</x:v>
+        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7" ht="15" customHeight="1">
@@ -4489,22 +4495,22 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>607</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>608</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>609</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="F109" s="1" t="s">
-        <x:v>611</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>614</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7" ht="15" customHeight="1">
@@ -4512,22 +4518,22 @@
         <x:v>107</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>613</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="D110" s="1" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="E110" s="1" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="F110" s="1" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="G110" s="1" t="s">
         <x:v>614</x:v>
-      </x:c>
-      <x:c r="D110" s="1" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="E110" s="1" t="s">
-        <x:v>616</x:v>
-      </x:c>
-      <x:c r="F110" s="1" t="s">
-        <x:v>617</x:v>
-      </x:c>
-      <x:c r="G110" s="1" t="s">
-        <x:v>612</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7" ht="15" customHeight="1">
@@ -4535,22 +4541,22 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>618</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>619</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>621</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="F111" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>623</x:v>
+        <x:v>625</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7" ht="15" customHeight="1">
@@ -4558,22 +4564,22 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>625</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>626</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>627</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="F112" s="1" t="s">
-        <x:v>628</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>629</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7" ht="15" customHeight="1">
@@ -4581,22 +4587,22 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="D113" s="1" t="s">
+        <x:v>634</x:v>
+      </x:c>
+      <x:c r="E113" s="1" t="s">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="F113" s="1" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="G113" s="1" t="s">
         <x:v>631</x:v>
-      </x:c>
-      <x:c r="D113" s="1" t="s">
-        <x:v>632</x:v>
-      </x:c>
-      <x:c r="E113" s="1" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="F113" s="1" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="G113" s="1" t="s">
-        <x:v>629</x:v>
       </x:c>
     </x:row>
     <x:row r="114" spans="1:7" ht="15" customHeight="1">
@@ -4604,22 +4610,22 @@
         <x:v>111</x:v>
       </x:c>
       <x:c r="B114" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="C114" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="D114" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="E114" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="F114" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="G114" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>551</x:v>
       </x:c>
     </x:row>
     <x:row r="115" spans="1:7" ht="15" customHeight="1">
